--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9598,8 +9598,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -9623,8 +9623,6 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -9699,16 +9697,6 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -9861,25 +9849,10 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC323E73-6D4D-472E-9769-DA43278CADDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E7086F0-770B-4323-8BF9-02EC28EAB4FC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958A80CB-35A6-4507-9FC9-D9DC95A13CE9}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A3E0F40-1F97-4B03-BCFA-8E42EFA81125}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9598,8 +9598,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2CD72C2-B736-4967-8C85-91B91269CC3D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D96E7E0B-08BA-476C-A963-DD6300BBC402}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958A80CB-35A6-4507-9FC9-D9DC95A13CE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18FED7D1-7230-489E-94E3-6DE882FD8AAE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F32684B-38D1-4211-815E-2266952D98F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F34CC130-73FC-4888-BFE6-A0E2070A7867}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D96E7E0B-08BA-476C-A963-DD6300BBC402}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA3F6157-610B-46B0-AA18-D5D89E09109B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18FED7D1-7230-489E-94E3-6DE882FD8AAE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BA5D94F-44DA-4426-9F65-69FADE7AFBE5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F34CC130-73FC-4888-BFE6-A0E2070A7867}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3181A298-8478-420B-A220-79AC8C88D15D}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA3F6157-610B-46B0-AA18-D5D89E09109B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{977D6F22-0296-482F-9D47-F6C692426C0F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BA5D94F-44DA-4426-9F65-69FADE7AFBE5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E06A503-94A2-41D5-91E1-977F171D1E85}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3181A298-8478-420B-A220-79AC8C88D15D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D69E5E4B-D925-41C5-82F7-6106BA30A23E}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{977D6F22-0296-482F-9D47-F6C692426C0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20A0D7E4-E2D2-4706-8F99-45FF058070E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E06A503-94A2-41D5-91E1-977F171D1E85}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1BB105A-180C-4B79-864E-4448B1502F24}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D69E5E4B-D925-41C5-82F7-6106BA30A23E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{158D3CAF-AAC7-4401-AEF6-B1E4ECD8ABC4}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20A0D7E4-E2D2-4706-8F99-45FF058070E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0931F70A-599F-4BA7-BA28-733AEC956F3D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1BB105A-180C-4B79-864E-4448B1502F24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6243130-445B-4049-A1A5-09D20B182AC2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{158D3CAF-AAC7-4401-AEF6-B1E4ECD8ABC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7A799F8-B0D5-4AA0-B511-9D6DBFA39240}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0931F70A-599F-4BA7-BA28-733AEC956F3D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51226F80-C1F4-46EB-82F6-73766F25BC49}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6243130-445B-4049-A1A5-09D20B182AC2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C41C5F4C-BE4B-4C3B-9B92-2EA1E41D5544}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7A799F8-B0D5-4AA0-B511-9D6DBFA39240}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD11EEA7-E7D2-4D95-A212-E1BFB31E0CCF}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51226F80-C1F4-46EB-82F6-73766F25BC49}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0239BEB4-ADE2-43C6-B0F9-F83CACF08AB1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C41C5F4C-BE4B-4C3B-9B92-2EA1E41D5544}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A15E234F-E6A7-45CC-9E22-B0B8FE3AE03B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD11EEA7-E7D2-4D95-A212-E1BFB31E0CCF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BE91B72-053F-41AB-9390-AE3B779DBB53}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0239BEB4-ADE2-43C6-B0F9-F83CACF08AB1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1F684CF-725F-49FD-BD2E-A74A4B981F48}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A15E234F-E6A7-45CC-9E22-B0B8FE3AE03B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC0AF7D6-0B77-46DE-9701-AD12548F41DC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BE91B72-053F-41AB-9390-AE3B779DBB53}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F7A82AE-0154-4506-B6AF-D6723DD803FD}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1F684CF-725F-49FD-BD2E-A74A4B981F48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C76AD2-AA97-451B-BF9B-5DBB64A076AD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC0AF7D6-0B77-46DE-9701-AD12548F41DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{045AD488-665D-417D-B447-F911854024D3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F7A82AE-0154-4506-B6AF-D6723DD803FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7364002-23D1-400E-B6BA-E15ED2A3FB22}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C76AD2-AA97-451B-BF9B-5DBB64A076AD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7112F6AB-00B0-475B-867D-5E2A75B61C45}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{045AD488-665D-417D-B447-F911854024D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{566FFD58-6BD6-4ABE-993B-D60327CA38AB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7364002-23D1-400E-B6BA-E15ED2A3FB22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9C228A1-2A94-4616-A95A-6C1B443C3931}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7112F6AB-00B0-475B-867D-5E2A75B61C45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{484E68FF-096A-4C13-BADE-E1DBBF5E1E28}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{566FFD58-6BD6-4ABE-993B-D60327CA38AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54F127F4-25BA-4B3D-838C-1C9B076078FA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9C228A1-2A94-4616-A95A-6C1B443C3931}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDE8DD04-4760-4551-8F9F-144AC6E68B3E}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{484E68FF-096A-4C13-BADE-E1DBBF5E1E28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EA03DAB-8591-4AF9-A480-E5F73137981F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54F127F4-25BA-4B3D-838C-1C9B076078FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57EBC26-3E74-46D5-B2D5-1130C8822058}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDE8DD04-4760-4551-8F9F-144AC6E68B3E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F02439EF-23E4-43EA-880B-E8D90EF760E2}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9873,13 +9873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EA03DAB-8591-4AF9-A480-E5F73137981F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FDC06F6-63EC-4C89-BFA8-69E4DEACA3ED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C57EBC26-3E74-46D5-B2D5-1130C8822058}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04448C68-C568-4779-A830-B3037BD49537}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F02439EF-23E4-43EA-880B-E8D90EF760E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E55ED338-84E1-4810-A5FF-26DE88EA7F56}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO103"/>
+  <dimension ref="A1:AO105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -517,7 +517,7 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Basal_metaboic_rate</t>
+          <t>Basal_metabolic_rate</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Neuronal_denisty</t>
+          <t>Neuronal_density</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Glial_cell_denisty</t>
+          <t>Glial_cell_density</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
@@ -574,7 +574,7 @@
         <v>27.5</v>
       </c>
       <c r="G2">
-        <v>1.36</v>
+        <v>1.3555</v>
       </c>
       <c r="I2">
         <v>49.5</v>
@@ -598,7 +598,7 @@
         <v>200</v>
       </c>
       <c r="S2">
-        <v>0.38</v>
+        <v>0.379</v>
       </c>
       <c r="T2">
         <v>400</v>
@@ -617,7 +617,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD2">
@@ -663,7 +663,7 @@
         <v>4.59</v>
       </c>
       <c r="K3">
-        <v>139.61</v>
+        <v>139.6125</v>
       </c>
       <c r="L3">
         <v>42</v>
@@ -687,13 +687,13 @@
         <v>22</v>
       </c>
       <c r="S3">
-        <v>1.38</v>
+        <v>1.375</v>
       </c>
       <c r="T3">
         <v>8.9</v>
       </c>
       <c r="V3">
-        <v>117.61</v>
+        <v>117.6125</v>
       </c>
       <c r="W3">
         <v>0.06</v>
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>314.67</v>
+        <v>314.6666667</v>
       </c>
       <c r="D4">
-        <v>2.41</v>
+        <v>2.406666667</v>
       </c>
       <c r="E4">
         <v>0.28</v>
@@ -762,7 +762,7 @@
         <v>2.99</v>
       </c>
       <c r="K4">
-        <v>90.95</v>
+        <v>90.94583333</v>
       </c>
       <c r="L4">
         <v>90</v>
@@ -783,16 +783,16 @@
         <v>25</v>
       </c>
       <c r="S4">
-        <v>5.36</v>
+        <v>5.365</v>
       </c>
       <c r="T4">
         <v>63.8</v>
       </c>
       <c r="V4">
-        <v>65.95</v>
+        <v>65.94583333</v>
       </c>
       <c r="W4">
-        <v>0.25</v>
+        <v>0.253</v>
       </c>
       <c r="Y4">
         <v>2</v>
@@ -850,7 +850,7 @@
         <v>2.42</v>
       </c>
       <c r="K5">
-        <v>73.61</v>
+        <v>73.60833332999999</v>
       </c>
       <c r="L5">
         <v>48</v>
@@ -871,13 +871,13 @@
         <v>20</v>
       </c>
       <c r="S5">
-        <v>2.12</v>
+        <v>2.125</v>
       </c>
       <c r="T5">
         <v>22.93</v>
       </c>
       <c r="V5">
-        <v>53.61</v>
+        <v>53.60833333</v>
       </c>
       <c r="Y5">
         <v>1</v>
@@ -920,7 +920,7 @@
         <v>21750</v>
       </c>
       <c r="D6">
-        <v>41.17</v>
+        <v>41.16666667</v>
       </c>
       <c r="E6">
         <v>13.9</v>
@@ -935,7 +935,7 @@
         <v>22.28</v>
       </c>
       <c r="K6">
-        <v>677.6799999999999</v>
+        <v>677.6833333</v>
       </c>
       <c r="L6">
         <v>639</v>
@@ -962,7 +962,7 @@
         <v>451</v>
       </c>
       <c r="V6">
-        <v>617.6799999999999</v>
+        <v>617.6833333</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AD6">
@@ -1025,7 +1025,7 @@
         <v>24.99</v>
       </c>
       <c r="K7">
-        <v>760.11</v>
+        <v>760.1125</v>
       </c>
       <c r="L7">
         <v>456</v>
@@ -1034,7 +1034,7 @@
         <v>456</v>
       </c>
       <c r="N7">
-        <v>136</v>
+        <v>136.5</v>
       </c>
       <c r="O7">
         <v>3.9</v>
@@ -1055,7 +1055,7 @@
         <v>8299</v>
       </c>
       <c r="V7">
-        <v>657.11</v>
+        <v>657.1125</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD7">
@@ -1202,7 +1202,7 @@
         <v>3.99</v>
       </c>
       <c r="K9">
-        <v>121.36</v>
+        <v>121.3625</v>
       </c>
       <c r="L9">
         <v>730</v>
@@ -1232,7 +1232,7 @@
         <v>214</v>
       </c>
       <c r="V9">
-        <v>95.36</v>
+        <v>95.3625</v>
       </c>
       <c r="W9">
         <v>1.65</v>
@@ -1278,7 +1278,7 @@
         <v>67</v>
       </c>
       <c r="G10">
-        <v>1.78</v>
+        <v>1.785</v>
       </c>
       <c r="I10">
         <v>37.8</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AD10">
@@ -1389,10 +1389,10 @@
         <v>1095</v>
       </c>
       <c r="L11">
-        <v>1246</v>
+        <v>1246.07</v>
       </c>
       <c r="M11">
-        <v>1246</v>
+        <v>1246.07</v>
       </c>
       <c r="N11">
         <v>167</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AD11">
@@ -1497,7 +1497,7 @@
         <v>2008</v>
       </c>
       <c r="N12">
-        <v>164</v>
+        <v>164.5</v>
       </c>
       <c r="O12">
         <v>1</v>
@@ -1506,10 +1506,10 @@
         <v>1</v>
       </c>
       <c r="Q12">
-        <v>730</v>
+        <v>730.5</v>
       </c>
       <c r="R12">
-        <v>168</v>
+        <v>168.3333333</v>
       </c>
       <c r="S12">
         <v>187.1</v>
@@ -1521,7 +1521,7 @@
         <v>3.44</v>
       </c>
       <c r="V12">
-        <v>1430.37</v>
+        <v>1430.366667</v>
       </c>
       <c r="W12">
         <v>120</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>91.20</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AD12">
@@ -1572,7 +1572,7 @@
         <v>159.4</v>
       </c>
       <c r="G13">
-        <v>2.14</v>
+        <v>2.1384</v>
       </c>
       <c r="I13">
         <v>40</v>
@@ -1584,13 +1584,13 @@
         <v>1460</v>
       </c>
       <c r="L13">
-        <v>2122</v>
+        <v>2122.11</v>
       </c>
       <c r="M13">
-        <v>2122</v>
+        <v>2122.11</v>
       </c>
       <c r="N13">
-        <v>198</v>
+        <v>197.5</v>
       </c>
       <c r="O13">
         <v>1</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AD13">
@@ -1665,13 +1665,13 @@
         <v>7992.75</v>
       </c>
       <c r="D14">
-        <v>103.38</v>
+        <v>103.375</v>
       </c>
       <c r="F14">
         <v>68733</v>
       </c>
       <c r="G14">
-        <v>1.86</v>
+        <v>1.865</v>
       </c>
       <c r="H14">
         <v>742</v>
@@ -1683,13 +1683,13 @@
         <v>49.05</v>
       </c>
       <c r="K14">
-        <v>1491.94</v>
+        <v>1491.9375</v>
       </c>
       <c r="L14">
-        <v>2525</v>
+        <v>2525.48</v>
       </c>
       <c r="M14">
-        <v>2525</v>
+        <v>2525.48</v>
       </c>
       <c r="N14">
         <v>175</v>
@@ -1710,7 +1710,7 @@
         <v>2.61</v>
       </c>
       <c r="V14">
-        <v>1126.94</v>
+        <v>1126.9375</v>
       </c>
       <c r="W14">
         <v>410</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AD14">
@@ -1769,7 +1769,7 @@
         <v>75</v>
       </c>
       <c r="G15">
-        <v>1.98</v>
+        <v>1.985</v>
       </c>
       <c r="I15">
         <v>37.5</v>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>36.90</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AD15">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>7102.83</v>
+        <v>7102.833333</v>
       </c>
       <c r="D16">
         <v>89.22</v>
@@ -1882,7 +1882,7 @@
         <v>50</v>
       </c>
       <c r="K16">
-        <v>1520.83</v>
+        <v>1520.833333</v>
       </c>
       <c r="L16">
         <v>1231</v>
@@ -1891,7 +1891,7 @@
         <v>2007</v>
       </c>
       <c r="N16">
-        <v>166</v>
+        <v>165.6666667</v>
       </c>
       <c r="O16">
         <v>1</v>
@@ -1900,13 +1900,13 @@
         <v>1</v>
       </c>
       <c r="Q16">
-        <v>404</v>
+        <v>404.5</v>
       </c>
       <c r="R16">
-        <v>292</v>
+        <v>292.5</v>
       </c>
       <c r="S16">
-        <v>485.82</v>
+        <v>485.825</v>
       </c>
       <c r="T16">
         <v>1435</v>
@@ -1915,7 +1915,7 @@
         <v>2.46</v>
       </c>
       <c r="V16">
-        <v>1228.33</v>
+        <v>1228.333333</v>
       </c>
       <c r="W16">
         <v>400</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>38.50</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AD16">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>7854.83</v>
+        <v>7854.833333</v>
       </c>
       <c r="D17">
         <v>76.75</v>
@@ -1984,7 +1984,7 @@
         <v>50906</v>
       </c>
       <c r="G17">
-        <v>1.8</v>
+        <v>1.805</v>
       </c>
       <c r="H17">
         <v>455</v>
@@ -1993,13 +1993,13 @@
         <v>45.45</v>
       </c>
       <c r="K17">
-        <v>1382.44</v>
+        <v>1382.4375</v>
       </c>
       <c r="R17">
-        <v>656</v>
+        <v>656.2</v>
       </c>
       <c r="V17">
-        <v>726.24</v>
+        <v>726.2375</v>
       </c>
       <c r="W17">
         <v>71</v>
@@ -2032,16 +2032,16 @@
         </is>
       </c>
       <c r="C18">
-        <v>8481.67</v>
+        <v>8481.666667</v>
       </c>
       <c r="D18">
-        <v>84.83</v>
+        <v>84.83333333</v>
       </c>
       <c r="F18">
         <v>48763</v>
       </c>
       <c r="G18">
-        <v>1.64</v>
+        <v>1.635</v>
       </c>
       <c r="H18">
         <v>911</v>
@@ -2059,7 +2059,7 @@
         <v>1460</v>
       </c>
       <c r="N18">
-        <v>190</v>
+        <v>190.5</v>
       </c>
       <c r="O18">
         <v>1</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>9.300000000000001</t>
         </is>
       </c>
       <c r="AD18">
@@ -2145,7 +2145,7 @@
         <v>103.5</v>
       </c>
       <c r="K19">
-        <v>3148.12</v>
+        <v>3148.125</v>
       </c>
       <c r="L19">
         <v>2829</v>
@@ -2154,7 +2154,7 @@
         <v>4015</v>
       </c>
       <c r="N19">
-        <v>264</v>
+        <v>264.5</v>
       </c>
       <c r="O19">
         <v>1</v>
@@ -2163,7 +2163,7 @@
         <v>0.3</v>
       </c>
       <c r="Q19">
-        <v>1404</v>
+        <v>1403.5</v>
       </c>
       <c r="R19">
         <v>1004</v>
@@ -2178,7 +2178,7 @@
         <v>6.58</v>
       </c>
       <c r="V19">
-        <v>2144.12</v>
+        <v>2144.125</v>
       </c>
       <c r="W19">
         <v>1800</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD19">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>61770.32</v>
+        <v>61770.315</v>
       </c>
       <c r="D20">
         <v>1300</v>
@@ -2267,7 +2267,7 @@
         <v>5110</v>
       </c>
       <c r="N20">
-        <v>275</v>
+        <v>274.78</v>
       </c>
       <c r="O20">
         <v>1</v>
@@ -2276,10 +2276,10 @@
         <v>0.3</v>
       </c>
       <c r="Q20">
-        <v>958</v>
+        <v>958.12</v>
       </c>
       <c r="R20">
-        <v>726</v>
+        <v>725.86</v>
       </c>
       <c r="S20">
         <v>3421</v>
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="C21">
-        <v>41057.09</v>
+        <v>41057.09091</v>
       </c>
       <c r="D21">
         <v>392.06</v>
@@ -2354,7 +2354,7 @@
         <v>291592</v>
       </c>
       <c r="G21">
-        <v>2.46</v>
+        <v>2.455</v>
       </c>
       <c r="H21">
         <v>1899</v>
@@ -2366,7 +2366,7 @@
         <v>164.8</v>
       </c>
       <c r="K21">
-        <v>5012.67</v>
+        <v>5012.666667</v>
       </c>
       <c r="L21">
         <v>3376</v>
@@ -2387,7 +2387,7 @@
         <v>1320</v>
       </c>
       <c r="R21">
-        <v>1580</v>
+        <v>1579.5</v>
       </c>
       <c r="S21">
         <v>1736.25</v>
@@ -2399,7 +2399,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="V21">
-        <v>3433.17</v>
+        <v>3433.166667</v>
       </c>
       <c r="W21">
         <v>1085</v>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>45.00</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AD21">
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>42447.67</v>
+        <v>42447.66667</v>
       </c>
       <c r="D22">
         <v>347.75</v>
@@ -2489,7 +2489,7 @@
         <v>2555</v>
       </c>
       <c r="N22">
-        <v>248</v>
+        <v>248.5</v>
       </c>
       <c r="O22">
         <v>1</v>
@@ -2501,7 +2501,7 @@
         <v>1787</v>
       </c>
       <c r="R22">
-        <v>1206</v>
+        <v>1206.25</v>
       </c>
       <c r="S22">
         <v>1654.5</v>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD22">
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="C23">
-        <v>5724.86</v>
+        <v>5724.857143</v>
       </c>
       <c r="D23">
         <v>101.52</v>
@@ -2582,7 +2582,7 @@
         <v>65800</v>
       </c>
       <c r="G23">
-        <v>1.86</v>
+        <v>1.855</v>
       </c>
       <c r="H23">
         <v>555</v>
@@ -2591,10 +2591,10 @@
         <v>44</v>
       </c>
       <c r="J23">
-        <v>101.19</v>
+        <v>101.1933333</v>
       </c>
       <c r="K23">
-        <v>3077.96</v>
+        <v>3077.963888</v>
       </c>
       <c r="L23">
         <v>2555</v>
@@ -2612,7 +2612,7 @@
         <v>0.5</v>
       </c>
       <c r="Q23">
-        <v>998</v>
+        <v>997.5</v>
       </c>
       <c r="R23">
         <v>626</v>
@@ -2627,7 +2627,7 @@
         <v>6.73</v>
       </c>
       <c r="V23">
-        <v>2451.96</v>
+        <v>2451.963888</v>
       </c>
       <c r="W23">
         <v>57</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AD23">
@@ -2678,7 +2678,7 @@
         <v>30.8</v>
       </c>
       <c r="G24">
-        <v>1.33</v>
+        <v>1.3275</v>
       </c>
       <c r="I24">
         <v>24.3</v>
@@ -2687,13 +2687,13 @@
         <v>45.5</v>
       </c>
       <c r="K24">
-        <v>1383.96</v>
+        <v>1383.958333</v>
       </c>
       <c r="L24">
-        <v>1578</v>
+        <v>1578.42</v>
       </c>
       <c r="M24">
-        <v>1578</v>
+        <v>1578.42</v>
       </c>
       <c r="N24">
         <v>186</v>
@@ -2705,7 +2705,7 @@
         <v>240</v>
       </c>
       <c r="R24">
-        <v>483</v>
+        <v>483.3333333</v>
       </c>
       <c r="S24">
         <v>380</v>
@@ -2717,7 +2717,7 @@
         <v>1.35</v>
       </c>
       <c r="V24">
-        <v>900.62</v>
+        <v>900.625</v>
       </c>
       <c r="W24">
         <v>31</v>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AD24">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="C25">
-        <v>5889.57</v>
+        <v>5889.571429</v>
       </c>
       <c r="D25">
         <v>54.95</v>
       </c>
       <c r="G25">
-        <v>1.46</v>
+        <v>1.465</v>
       </c>
       <c r="I25">
         <v>25</v>
@@ -2786,13 +2786,13 @@
         <v>58.5</v>
       </c>
       <c r="K25">
-        <v>1779.38</v>
+        <v>1779.375</v>
       </c>
       <c r="L25">
         <v>1475</v>
       </c>
       <c r="N25">
-        <v>190</v>
+        <v>190.5</v>
       </c>
       <c r="O25">
         <v>1.42</v>
@@ -2813,7 +2813,7 @@
         <v>3.04</v>
       </c>
       <c r="V25">
-        <v>1407.38</v>
+        <v>1407.375</v>
       </c>
       <c r="W25">
         <v>23</v>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AD25">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>8447.43</v>
+        <v>8447.428571</v>
       </c>
       <c r="D26">
         <v>108.5</v>
@@ -2882,7 +2882,7 @@
         <v>1280</v>
       </c>
       <c r="N26">
-        <v>230</v>
+        <v>229.5</v>
       </c>
       <c r="O26">
         <v>1</v>
@@ -2894,16 +2894,16 @@
         <v>680</v>
       </c>
       <c r="R26">
-        <v>788</v>
+        <v>788.3333333</v>
       </c>
       <c r="S26">
-        <v>459.38</v>
+        <v>459.375</v>
       </c>
       <c r="T26">
         <v>3790</v>
       </c>
       <c r="V26">
-        <v>1036.67</v>
+        <v>1036.666667</v>
       </c>
       <c r="W26">
         <v>225</v>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD26">
@@ -2948,7 +2948,7 @@
         <v>5959</v>
       </c>
       <c r="D27">
-        <v>95.58</v>
+        <v>95.575</v>
       </c>
       <c r="F27">
         <v>65873</v>
@@ -2966,7 +2966,7 @@
         <v>75.5</v>
       </c>
       <c r="K27">
-        <v>2296.46</v>
+        <v>2296.458333</v>
       </c>
       <c r="L27">
         <v>2555</v>
@@ -2987,7 +2987,7 @@
         <v>288</v>
       </c>
       <c r="R27">
-        <v>391</v>
+        <v>391.3333333</v>
       </c>
       <c r="S27">
         <v>393</v>
@@ -2996,7 +2996,7 @@
         <v>3.53</v>
       </c>
       <c r="V27">
-        <v>1905.12</v>
+        <v>1905.125</v>
       </c>
       <c r="W27">
         <v>400</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AD27">
@@ -3047,7 +3047,7 @@
         <v>19</v>
       </c>
       <c r="G28">
-        <v>1.25</v>
+        <v>1.2537</v>
       </c>
       <c r="I28">
         <v>24.6</v>
@@ -3059,10 +3059,10 @@
         <v>1095</v>
       </c>
       <c r="L28">
-        <v>1263</v>
+        <v>1262.74</v>
       </c>
       <c r="M28">
-        <v>1263</v>
+        <v>1262.74</v>
       </c>
       <c r="N28">
         <v>164</v>
@@ -3160,10 +3160,10 @@
         <v>25.25</v>
       </c>
       <c r="J29">
-        <v>28.57</v>
+        <v>28.56666667</v>
       </c>
       <c r="K29">
-        <v>868.9</v>
+        <v>868.9027779</v>
       </c>
       <c r="L29">
         <v>821</v>
@@ -3172,7 +3172,7 @@
         <v>730</v>
       </c>
       <c r="N29">
-        <v>138</v>
+        <v>137.5</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -3184,7 +3184,7 @@
         <v>269</v>
       </c>
       <c r="R29">
-        <v>110</v>
+        <v>110.3333333</v>
       </c>
       <c r="S29">
         <v>91.25</v>
@@ -3196,7 +3196,7 @@
         <v>1.81</v>
       </c>
       <c r="V29">
-        <v>758.5700000000001</v>
+        <v>758.5694446</v>
       </c>
       <c r="W29">
         <v>8.5</v>
@@ -3265,7 +3265,7 @@
         <v>6476</v>
       </c>
       <c r="G30">
-        <v>1.26</v>
+        <v>1.255</v>
       </c>
       <c r="H30">
         <v>47.9</v>
@@ -3274,13 +3274,13 @@
         <v>17.9</v>
       </c>
       <c r="J30">
-        <v>15.73</v>
+        <v>15.73333333</v>
       </c>
       <c r="K30">
-        <v>478.56</v>
+        <v>478.5555555</v>
       </c>
       <c r="L30">
-        <v>310</v>
+        <v>309.5</v>
       </c>
       <c r="M30">
         <v>395</v>
@@ -3295,13 +3295,13 @@
         <v>1.2</v>
       </c>
       <c r="Q30">
-        <v>207</v>
+        <v>206.6666667</v>
       </c>
       <c r="R30">
-        <v>69</v>
+        <v>69.25</v>
       </c>
       <c r="S30">
-        <v>49.51</v>
+        <v>49.5125</v>
       </c>
       <c r="T30">
         <v>167.5</v>
@@ -3310,7 +3310,7 @@
         <v>0.7</v>
       </c>
       <c r="V30">
-        <v>409.31</v>
+        <v>409.3055555</v>
       </c>
       <c r="W30">
         <v>45</v>
@@ -3360,7 +3360,7 @@
         <v>288.12</v>
       </c>
       <c r="D31">
-        <v>7.61</v>
+        <v>7.614285714</v>
       </c>
       <c r="E31">
         <v>3.63</v>
@@ -3381,7 +3381,7 @@
         <v>18.25</v>
       </c>
       <c r="K31">
-        <v>555.1</v>
+        <v>555.1041667</v>
       </c>
       <c r="L31">
         <v>421</v>
@@ -3402,19 +3402,19 @@
         <v>163</v>
       </c>
       <c r="R31">
-        <v>70</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="S31">
-        <v>27.93</v>
+        <v>27.9325</v>
       </c>
       <c r="T31">
-        <v>107.78</v>
+        <v>107.785</v>
       </c>
       <c r="U31">
         <v>0.85</v>
       </c>
       <c r="V31">
-        <v>484.7</v>
+        <v>484.7041667</v>
       </c>
       <c r="W31">
         <v>6.5</v>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>8.550000000000001</t>
         </is>
       </c>
       <c r="AF31">
@@ -3471,7 +3471,7 @@
         <v>5883</v>
       </c>
       <c r="G32">
-        <v>1.2</v>
+        <v>1.195</v>
       </c>
       <c r="H32">
         <v>251</v>
@@ -3489,7 +3489,7 @@
         <v>608</v>
       </c>
       <c r="N32">
-        <v>140</v>
+        <v>140.5</v>
       </c>
       <c r="O32">
         <v>2</v>
@@ -3501,7 +3501,7 @@
         <v>240</v>
       </c>
       <c r="R32">
-        <v>70</v>
+        <v>70.5</v>
       </c>
       <c r="S32">
         <v>38</v>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>368.83</v>
+        <v>368.8333333</v>
       </c>
       <c r="D33">
         <v>9.800000000000001</v>
@@ -3555,7 +3555,7 @@
         <v>5894</v>
       </c>
       <c r="G33">
-        <v>1.2</v>
+        <v>1.195</v>
       </c>
       <c r="I33">
         <v>23.08</v>
@@ -3573,7 +3573,7 @@
         <v>550</v>
       </c>
       <c r="N33">
-        <v>162</v>
+        <v>161.5</v>
       </c>
       <c r="O33">
         <v>1.9</v>
@@ -3648,7 +3648,7 @@
         <v>2482.8</v>
       </c>
       <c r="D34">
-        <v>71.23</v>
+        <v>71.23333332999999</v>
       </c>
       <c r="E34">
         <v>33.65</v>
@@ -3663,7 +3663,7 @@
         <v>48.1</v>
       </c>
       <c r="K34">
-        <v>1463.04</v>
+        <v>1463.041667</v>
       </c>
       <c r="L34">
         <v>1310</v>
@@ -3672,7 +3672,7 @@
         <v>1310</v>
       </c>
       <c r="N34">
-        <v>158</v>
+        <v>158.3333333</v>
       </c>
       <c r="O34">
         <v>1</v>
@@ -3684,7 +3684,7 @@
         <v>546</v>
       </c>
       <c r="R34">
-        <v>271</v>
+        <v>270.6</v>
       </c>
       <c r="S34">
         <v>230.85</v>
@@ -3696,7 +3696,7 @@
         <v>2.85</v>
       </c>
       <c r="V34">
-        <v>1192.44</v>
+        <v>1192.441667</v>
       </c>
       <c r="W34">
         <v>15</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AD34">
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>115.88</v>
+        <v>115.875</v>
       </c>
       <c r="D36">
         <v>3</v>
@@ -3866,7 +3866,7 @@
         <v>2.09</v>
       </c>
       <c r="G36">
-        <v>1.08</v>
+        <v>1.075</v>
       </c>
       <c r="I36">
         <v>12</v>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD36">
@@ -3950,7 +3950,7 @@
         <v>112.05</v>
       </c>
       <c r="D37">
-        <v>3.83</v>
+        <v>3.833333333</v>
       </c>
       <c r="G37">
         <v>1.1</v>
@@ -3962,7 +3962,7 @@
         <v>30.2</v>
       </c>
       <c r="K37">
-        <v>918.58</v>
+        <v>918.5833333</v>
       </c>
       <c r="N37">
         <v>179</v>
@@ -3974,10 +3974,10 @@
         <v>240</v>
       </c>
       <c r="R37">
-        <v>81</v>
+        <v>81.33333333</v>
       </c>
       <c r="S37">
-        <v>24.92</v>
+        <v>24.925</v>
       </c>
       <c r="U37">
         <v>1.82</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD37">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="C38">
-        <v>71.83</v>
+        <v>71.828</v>
       </c>
       <c r="D38">
-        <v>1.85</v>
+        <v>1.846666667</v>
       </c>
       <c r="F38">
         <v>740</v>
@@ -4057,10 +4057,10 @@
         <v>15.5</v>
       </c>
       <c r="J38">
-        <v>14.83</v>
+        <v>14.83333333</v>
       </c>
       <c r="K38">
-        <v>451.18</v>
+        <v>451.1805555</v>
       </c>
       <c r="L38">
         <v>243</v>
@@ -4069,7 +4069,7 @@
         <v>243</v>
       </c>
       <c r="N38">
-        <v>61</v>
+        <v>60.75</v>
       </c>
       <c r="O38">
         <v>2</v>
@@ -4084,13 +4084,13 @@
         <v>39</v>
       </c>
       <c r="S38">
-        <v>5.52</v>
+        <v>5.525</v>
       </c>
       <c r="U38">
         <v>0.73</v>
       </c>
       <c r="V38">
-        <v>412.18</v>
+        <v>412.1805555</v>
       </c>
       <c r="W38">
         <v>2</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD38">
@@ -4153,7 +4153,7 @@
         <v>433.25</v>
       </c>
       <c r="D39">
-        <v>6.43</v>
+        <v>6.433333333</v>
       </c>
       <c r="F39">
         <v>2938</v>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD39">
@@ -4237,7 +4237,7 @@
         <v>214</v>
       </c>
       <c r="D40">
-        <v>3.01</v>
+        <v>3.013333333</v>
       </c>
       <c r="F40">
         <v>1221</v>
@@ -4252,10 +4252,10 @@
         <v>19.25</v>
       </c>
       <c r="J40">
-        <v>14.33</v>
+        <v>14.33333333</v>
       </c>
       <c r="K40">
-        <v>435.97</v>
+        <v>435.9722221</v>
       </c>
       <c r="L40">
         <v>365</v>
@@ -4264,7 +4264,7 @@
         <v>730</v>
       </c>
       <c r="N40">
-        <v>62</v>
+        <v>61.66666667</v>
       </c>
       <c r="O40">
         <v>2.25</v>
@@ -4276,7 +4276,7 @@
         <v>365</v>
       </c>
       <c r="R40">
-        <v>62</v>
+        <v>61.5</v>
       </c>
       <c r="S40">
         <v>19</v>
@@ -4285,7 +4285,7 @@
         <v>0.86</v>
       </c>
       <c r="V40">
-        <v>374.47</v>
+        <v>374.4722221</v>
       </c>
       <c r="W40">
         <v>4</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD40">
@@ -4342,16 +4342,16 @@
         </is>
       </c>
       <c r="C41">
-        <v>1200.14</v>
+        <v>1200.1428</v>
       </c>
       <c r="D41">
-        <v>10.65</v>
+        <v>10.6475</v>
       </c>
       <c r="F41">
         <v>4813</v>
       </c>
       <c r="G41">
-        <v>1.26</v>
+        <v>1.255</v>
       </c>
       <c r="H41">
         <v>172</v>
@@ -4360,7 +4360,7 @@
         <v>30.9</v>
       </c>
       <c r="K41">
-        <v>939.88</v>
+        <v>939.875</v>
       </c>
       <c r="N41">
         <v>135</v>
@@ -4381,7 +4381,7 @@
         <v>500</v>
       </c>
       <c r="V41">
-        <v>774.88</v>
+        <v>774.875</v>
       </c>
       <c r="W41">
         <v>1.5</v>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD41">
@@ -4423,16 +4423,16 @@
         </is>
       </c>
       <c r="C42">
-        <v>832.33</v>
+        <v>832.333</v>
       </c>
       <c r="D42">
-        <v>9.68</v>
+        <v>9.685</v>
       </c>
       <c r="F42">
         <v>4443</v>
       </c>
       <c r="G42">
-        <v>1.14</v>
+        <v>1.145</v>
       </c>
       <c r="H42">
         <v>73.7</v>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF42">
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="C43">
-        <v>3547.12</v>
+        <v>3547.125</v>
       </c>
       <c r="D43">
         <v>26.9</v>
@@ -4489,7 +4489,7 @@
         <v>13170</v>
       </c>
       <c r="G43">
-        <v>1.34</v>
+        <v>1.345</v>
       </c>
       <c r="H43">
         <v>231</v>
@@ -4498,10 +4498,10 @@
         <v>20.6</v>
       </c>
       <c r="J43">
-        <v>43.47</v>
+        <v>43.46666667</v>
       </c>
       <c r="K43">
-        <v>1322.11</v>
+        <v>1322.111111</v>
       </c>
       <c r="L43">
         <v>912</v>
@@ -4510,7 +4510,7 @@
         <v>912</v>
       </c>
       <c r="N43">
-        <v>147</v>
+        <v>146.75</v>
       </c>
       <c r="O43">
         <v>1</v>
@@ -4519,10 +4519,10 @@
         <v>1</v>
       </c>
       <c r="Q43">
-        <v>448</v>
+        <v>448.5</v>
       </c>
       <c r="R43">
-        <v>173</v>
+        <v>173.25</v>
       </c>
       <c r="S43">
         <v>94.15000000000001</v>
@@ -4534,7 +4534,7 @@
         <v>2.62</v>
       </c>
       <c r="V43">
-        <v>1148.86</v>
+        <v>1148.861111</v>
       </c>
       <c r="W43">
         <v>8.5</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AD43">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="C44">
-        <v>7410.83</v>
+        <v>7410.8333</v>
       </c>
       <c r="D44">
         <v>37.35</v>
@@ -4594,7 +4594,7 @@
         <v>20114</v>
       </c>
       <c r="G44">
-        <v>1.46</v>
+        <v>1.455</v>
       </c>
       <c r="H44">
         <v>330</v>
@@ -4615,7 +4615,7 @@
         <v>2008</v>
       </c>
       <c r="N44">
-        <v>160</v>
+        <v>159.5</v>
       </c>
       <c r="O44">
         <v>1</v>
@@ -4627,13 +4627,13 @@
         <v>906</v>
       </c>
       <c r="R44">
-        <v>364</v>
+        <v>364.3333333</v>
       </c>
       <c r="S44">
         <v>300</v>
       </c>
       <c r="V44">
-        <v>2190.67</v>
+        <v>2190.666667</v>
       </c>
       <c r="W44">
         <v>18</v>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AD44">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="C45">
-        <v>2640.28</v>
+        <v>2640.285</v>
       </c>
       <c r="D45">
-        <v>44.89</v>
+        <v>44.8875</v>
       </c>
       <c r="F45">
         <v>22127</v>
@@ -4699,13 +4699,13 @@
         <v>35.5</v>
       </c>
       <c r="K45">
-        <v>1079.79</v>
+        <v>1079.791667</v>
       </c>
       <c r="L45">
         <v>882</v>
       </c>
       <c r="N45">
-        <v>164</v>
+        <v>164.5</v>
       </c>
       <c r="O45">
         <v>1</v>
@@ -4720,7 +4720,7 @@
         <v>244</v>
       </c>
       <c r="S45">
-        <v>119.33</v>
+        <v>119.3333333</v>
       </c>
       <c r="T45">
         <v>1535</v>
@@ -4729,7 +4729,7 @@
         <v>2.04</v>
       </c>
       <c r="V45">
-        <v>835.79</v>
+        <v>835.7916667</v>
       </c>
       <c r="W45">
         <v>11</v>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD45">
@@ -4798,10 +4798,10 @@
         <v>36</v>
       </c>
       <c r="J46">
-        <v>29.88</v>
+        <v>29.875</v>
       </c>
       <c r="K46">
-        <v>908.7</v>
+        <v>908.6979167</v>
       </c>
       <c r="L46">
         <v>548</v>
@@ -4831,7 +4831,7 @@
         <v>1.46</v>
       </c>
       <c r="V46">
-        <v>749.7</v>
+        <v>749.6979167</v>
       </c>
       <c r="W46">
         <v>8.75</v>
@@ -4891,7 +4891,7 @@
         <v>30.1</v>
       </c>
       <c r="K47">
-        <v>915.54</v>
+        <v>915.5416667</v>
       </c>
       <c r="L47">
         <v>550</v>
@@ -4900,7 +4900,7 @@
         <v>550</v>
       </c>
       <c r="N47">
-        <v>128</v>
+        <v>127.6666667</v>
       </c>
       <c r="O47">
         <v>1.05</v>
@@ -4921,7 +4921,7 @@
         <v>1.75</v>
       </c>
       <c r="V47">
-        <v>763.54</v>
+        <v>763.5416667</v>
       </c>
       <c r="W47">
         <v>70</v>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AD47">
@@ -4987,7 +4987,7 @@
         <v>8.77</v>
       </c>
       <c r="G48">
-        <v>1.32</v>
+        <v>1.325</v>
       </c>
       <c r="I48">
         <v>30</v>
@@ -4996,7 +4996,7 @@
         <v>29.72</v>
       </c>
       <c r="K48">
-        <v>903.98</v>
+        <v>903.9833333</v>
       </c>
       <c r="L48">
         <v>595</v>
@@ -5005,22 +5005,22 @@
         <v>912</v>
       </c>
       <c r="N48">
-        <v>135</v>
+        <v>135.3333333</v>
       </c>
       <c r="O48">
-        <v>1.13</v>
+        <v>1.133333333</v>
       </c>
       <c r="P48">
         <v>0.9</v>
       </c>
       <c r="Q48">
-        <v>434</v>
+        <v>433.6666667</v>
       </c>
       <c r="R48">
-        <v>140</v>
+        <v>139.6666667</v>
       </c>
       <c r="S48">
-        <v>63.52</v>
+        <v>63.516</v>
       </c>
       <c r="T48">
         <v>1080</v>
@@ -5029,7 +5029,7 @@
         <v>1.35</v>
       </c>
       <c r="V48">
-        <v>764.3200000000001</v>
+        <v>764.3166666</v>
       </c>
       <c r="W48">
         <v>35</v>
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="C49">
-        <v>3344.86</v>
+        <v>3344.857</v>
       </c>
       <c r="D49">
-        <v>49.82</v>
+        <v>49.825</v>
       </c>
       <c r="E49">
         <v>10.59</v>
@@ -5101,7 +5101,7 @@
         <v>15293</v>
       </c>
       <c r="G49">
-        <v>1.32</v>
+        <v>1.315</v>
       </c>
       <c r="H49">
         <v>299</v>
@@ -5113,7 +5113,7 @@
         <v>23.3</v>
       </c>
       <c r="K49">
-        <v>708.71</v>
+        <v>708.7083333</v>
       </c>
       <c r="L49">
         <v>604</v>
@@ -5122,7 +5122,7 @@
         <v>608</v>
       </c>
       <c r="N49">
-        <v>120</v>
+        <v>119.5</v>
       </c>
       <c r="O49">
         <v>2.1</v>
@@ -5134,7 +5134,7 @@
         <v>365</v>
       </c>
       <c r="R49">
-        <v>109</v>
+        <v>109.25</v>
       </c>
       <c r="S49">
         <v>88.2</v>
@@ -5143,7 +5143,7 @@
         <v>2696.5</v>
       </c>
       <c r="V49">
-        <v>599.46</v>
+        <v>599.4583333</v>
       </c>
       <c r="W49">
         <v>25.8</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AD49">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="C50">
-        <v>821.89</v>
+        <v>821.8933</v>
       </c>
       <c r="D50">
         <v>7.5</v>
@@ -5203,7 +5203,7 @@
         <v>3282</v>
       </c>
       <c r="G50">
-        <v>1.14</v>
+        <v>1.135</v>
       </c>
       <c r="H50">
         <v>76.5</v>
@@ -5212,7 +5212,7 @@
         <v>19.5</v>
       </c>
       <c r="K50">
-        <v>593.12</v>
+        <v>593.125</v>
       </c>
       <c r="L50">
         <v>595</v>
@@ -5239,7 +5239,7 @@
         <v>250</v>
       </c>
       <c r="V50">
-        <v>472.12</v>
+        <v>472.125</v>
       </c>
       <c r="Y50">
         <v>1</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF50">
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="C51">
-        <v>1008.43</v>
+        <v>1008.4285</v>
       </c>
       <c r="D51">
         <v>13.54</v>
@@ -5281,7 +5281,7 @@
         <v>6683</v>
       </c>
       <c r="G51">
-        <v>1.26</v>
+        <v>1.265</v>
       </c>
       <c r="H51">
         <v>127</v>
@@ -5293,7 +5293,7 @@
         <v>24.55</v>
       </c>
       <c r="K51">
-        <v>746.73</v>
+        <v>746.7291667</v>
       </c>
       <c r="L51">
         <v>547</v>
@@ -5314,7 +5314,7 @@
         <v>304</v>
       </c>
       <c r="R51">
-        <v>142</v>
+        <v>142.25</v>
       </c>
       <c r="S51">
         <v>40.55</v>
@@ -5323,7 +5323,7 @@
         <v>1.09</v>
       </c>
       <c r="V51">
-        <v>604.48</v>
+        <v>604.4791667</v>
       </c>
       <c r="W51">
         <v>12</v>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD51">
@@ -5374,7 +5374,7 @@
         <v>281.44</v>
       </c>
       <c r="D52">
-        <v>6.63</v>
+        <v>6.633333333</v>
       </c>
       <c r="E52">
         <v>2.69</v>
@@ -5383,7 +5383,7 @@
         <v>3524</v>
       </c>
       <c r="G52">
-        <v>1.28</v>
+        <v>1.285</v>
       </c>
       <c r="H52">
         <v>51.6</v>
@@ -5404,7 +5404,7 @@
         <v>365</v>
       </c>
       <c r="N52">
-        <v>166</v>
+        <v>165.75</v>
       </c>
       <c r="O52">
         <v>1.45</v>
@@ -5419,7 +5419,7 @@
         <v>160</v>
       </c>
       <c r="S52">
-        <v>11.18</v>
+        <v>11.175</v>
       </c>
       <c r="T52">
         <v>139</v>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD52">
@@ -5476,19 +5476,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>828.1900000000001</v>
+        <v>828.1875</v>
       </c>
       <c r="D53">
-        <v>11.73</v>
+        <v>11.73333333</v>
       </c>
       <c r="E53">
         <v>4</v>
       </c>
       <c r="F53">
-        <v>6.19</v>
+        <v>6.192</v>
       </c>
       <c r="G53">
-        <v>1.2</v>
+        <v>1.205</v>
       </c>
       <c r="H53">
         <v>142</v>
@@ -5500,7 +5500,7 @@
         <v>25.3</v>
       </c>
       <c r="K53">
-        <v>769.54</v>
+        <v>769.5416667</v>
       </c>
       <c r="L53">
         <v>578</v>
@@ -5515,10 +5515,10 @@
         <v>1</v>
       </c>
       <c r="Q53">
-        <v>428</v>
+        <v>428.5</v>
       </c>
       <c r="R53">
-        <v>157</v>
+        <v>157.25</v>
       </c>
       <c r="S53">
         <v>46.16</v>
@@ -5530,7 +5530,7 @@
         <v>1.09</v>
       </c>
       <c r="V53">
-        <v>612.29</v>
+        <v>612.2916667</v>
       </c>
       <c r="W53">
         <v>5</v>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD53">
@@ -5620,7 +5620,7 @@
         <v>300</v>
       </c>
       <c r="N54">
-        <v>131</v>
+        <v>130.6666667</v>
       </c>
       <c r="O54">
         <v>1.55</v>
@@ -5629,10 +5629,10 @@
         <v>2</v>
       </c>
       <c r="Q54">
-        <v>242</v>
+        <v>242.5</v>
       </c>
       <c r="R54">
-        <v>87</v>
+        <v>87.33333333</v>
       </c>
       <c r="S54">
         <v>15.55</v>
@@ -5644,7 +5644,7 @@
         <v>0.74</v>
       </c>
       <c r="V54">
-        <v>259.42</v>
+        <v>259.4166667</v>
       </c>
       <c r="W54">
         <v>11</v>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AD54">
@@ -5673,7 +5673,7 @@
         <v>2</v>
       </c>
       <c r="AG54">
-        <v>180.22</v>
+        <v>180.225</v>
       </c>
       <c r="AJ54">
         <v>4</v>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="C55">
-        <v>952.4299999999999</v>
+        <v>952.428</v>
       </c>
       <c r="D55">
         <v>10.6</v>
@@ -5715,7 +5715,7 @@
         <v>4723</v>
       </c>
       <c r="G55">
-        <v>1.26</v>
+        <v>1.255</v>
       </c>
       <c r="H55">
         <v>147</v>
@@ -5727,7 +5727,7 @@
         <v>23</v>
       </c>
       <c r="K55">
-        <v>699.58</v>
+        <v>699.5833333</v>
       </c>
       <c r="L55">
         <v>430</v>
@@ -5739,13 +5739,13 @@
         <v>134</v>
       </c>
       <c r="O55">
-        <v>1.53</v>
+        <v>1.533333333</v>
       </c>
       <c r="P55">
         <v>1</v>
       </c>
       <c r="Q55">
-        <v>281</v>
+        <v>281.3333333</v>
       </c>
       <c r="R55">
         <v>121</v>
@@ -5760,7 +5760,7 @@
         <v>1.47</v>
       </c>
       <c r="V55">
-        <v>578.58</v>
+        <v>578.5833333</v>
       </c>
       <c r="W55">
         <v>10</v>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AD55">
@@ -5808,10 +5808,10 @@
         <v>71.5</v>
       </c>
       <c r="D56">
-        <v>3.34</v>
+        <v>3.345</v>
       </c>
       <c r="E56">
-        <v>1.2</v>
+        <v>1.199</v>
       </c>
       <c r="F56">
         <v>1568</v>
@@ -5829,7 +5829,7 @@
         <v>21.4</v>
       </c>
       <c r="K56">
-        <v>650.92</v>
+        <v>650.9166667</v>
       </c>
       <c r="L56">
         <v>240</v>
@@ -5838,7 +5838,7 @@
         <v>274</v>
       </c>
       <c r="N56">
-        <v>110</v>
+        <v>110.3333333</v>
       </c>
       <c r="O56">
         <v>1.6</v>
@@ -5853,10 +5853,10 @@
         <v>45</v>
       </c>
       <c r="S56">
-        <v>8.470000000000001</v>
+        <v>8.466666667</v>
       </c>
       <c r="V56">
-        <v>605.92</v>
+        <v>605.9166667</v>
       </c>
       <c r="W56">
         <v>1</v>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AD56">
@@ -5904,7 +5904,7 @@
         <v>6.2</v>
       </c>
       <c r="G57">
-        <v>1.34</v>
+        <v>1.343</v>
       </c>
       <c r="N57">
         <v>105</v>
@@ -5952,16 +5952,16 @@
         </is>
       </c>
       <c r="C58">
-        <v>173.33</v>
+        <v>173.3333333</v>
       </c>
       <c r="D58">
-        <v>3.03</v>
+        <v>3.034</v>
       </c>
       <c r="E58">
         <v>0.53</v>
       </c>
       <c r="G58">
-        <v>1.06</v>
+        <v>1.062</v>
       </c>
       <c r="I58">
         <v>12.4</v>
@@ -6046,13 +6046,13 @@
         </is>
       </c>
       <c r="C59">
-        <v>63966.67</v>
+        <v>63966.66667</v>
       </c>
       <c r="D59">
         <v>125</v>
       </c>
       <c r="E59">
-        <v>47.82</v>
+        <v>47.825</v>
       </c>
       <c r="G59">
         <v>1.94</v>
@@ -6073,7 +6073,7 @@
         <v>914</v>
       </c>
       <c r="N59">
-        <v>149</v>
+        <v>148.655</v>
       </c>
       <c r="O59">
         <v>1.58</v>
@@ -6125,16 +6125,16 @@
         </is>
       </c>
       <c r="C60">
-        <v>38111.11</v>
+        <v>38111.111</v>
       </c>
       <c r="D60">
         <v>106</v>
       </c>
       <c r="E60">
-        <v>53.36</v>
+        <v>53.365</v>
       </c>
       <c r="G60">
-        <v>2.28</v>
+        <v>2.278</v>
       </c>
       <c r="I60">
         <v>20.8</v>
@@ -6143,7 +6143,7 @@
         <v>21.99</v>
       </c>
       <c r="K60">
-        <v>668.86</v>
+        <v>668.8625</v>
       </c>
       <c r="L60">
         <v>406</v>
@@ -6152,10 +6152,10 @@
         <v>685</v>
       </c>
       <c r="N60">
-        <v>155</v>
+        <v>154.874</v>
       </c>
       <c r="O60">
-        <v>1.38</v>
+        <v>1.375</v>
       </c>
       <c r="P60">
         <v>1</v>
@@ -6170,7 +6170,7 @@
         <v>2215</v>
       </c>
       <c r="V60">
-        <v>508.86</v>
+        <v>508.8625</v>
       </c>
       <c r="W60">
         <v>4724</v>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="C61">
-        <v>596666.67</v>
+        <v>596666.6666999999</v>
       </c>
       <c r="D61">
         <v>462</v>
@@ -6219,13 +6219,13 @@
         <v>548</v>
       </c>
       <c r="N61">
-        <v>280</v>
+        <v>279.6666667</v>
       </c>
       <c r="O61">
         <v>1</v>
       </c>
       <c r="S61">
-        <v>26122.22</v>
+        <v>26122.22333</v>
       </c>
       <c r="AA61">
         <v>2</v>
@@ -6262,7 +6262,7 @@
         <v>15.22</v>
       </c>
       <c r="K62">
-        <v>462.94</v>
+        <v>462.9416667</v>
       </c>
       <c r="L62">
         <v>309</v>
@@ -6292,7 +6292,7 @@
         <v>36000</v>
       </c>
       <c r="V62">
-        <v>333.94</v>
+        <v>333.9416667</v>
       </c>
       <c r="W62">
         <v>229</v>
@@ -6358,7 +6358,7 @@
         <v>1461</v>
       </c>
       <c r="N63">
-        <v>333</v>
+        <v>333.28</v>
       </c>
       <c r="O63">
         <v>1</v>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD63">
@@ -6506,7 +6506,7 @@
         <v>3689</v>
       </c>
       <c r="N65">
-        <v>362</v>
+        <v>362.5</v>
       </c>
       <c r="O65">
         <v>1</v>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD65">
@@ -6636,7 +6636,7 @@
         <v>725999.99</v>
       </c>
       <c r="D67">
-        <v>2886.3</v>
+        <v>2886.296</v>
       </c>
       <c r="G67">
         <v>5.24</v>
@@ -6700,7 +6700,7 @@
         <v>425000</v>
       </c>
       <c r="D68">
-        <v>1645.17</v>
+        <v>1645.168</v>
       </c>
       <c r="G68">
         <v>4.29</v>
@@ -6757,16 +6757,16 @@
         <v>2.16</v>
       </c>
       <c r="N69">
-        <v>117</v>
+        <v>116.645</v>
       </c>
       <c r="O69">
         <v>8</v>
       </c>
       <c r="P69">
-        <v>5.38</v>
+        <v>5.375</v>
       </c>
       <c r="R69">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="S69">
         <v>1215</v>
@@ -6806,7 +6806,7 @@
         <v>107250</v>
       </c>
       <c r="D70">
-        <v>216.77</v>
+        <v>216.7666667</v>
       </c>
       <c r="E70">
         <v>164.45</v>
@@ -6821,7 +6821,7 @@
         <v>23.98</v>
       </c>
       <c r="K70">
-        <v>729.39</v>
+        <v>729.3916667</v>
       </c>
       <c r="L70">
         <v>800</v>
@@ -6830,7 +6830,7 @@
         <v>800</v>
       </c>
       <c r="N70">
-        <v>332</v>
+        <v>332.05</v>
       </c>
       <c r="O70">
         <v>1</v>
@@ -6848,7 +6848,7 @@
         <v>29000</v>
       </c>
       <c r="V70">
-        <v>577.39</v>
+        <v>577.3916667</v>
       </c>
       <c r="Z70">
         <v>2</v>
@@ -7139,10 +7139,10 @@
         <v>365</v>
       </c>
       <c r="N74">
-        <v>64</v>
+        <v>63.915</v>
       </c>
       <c r="O74">
-        <v>3.44</v>
+        <v>3.445</v>
       </c>
       <c r="P74">
         <v>1</v>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD74">
@@ -7235,7 +7235,7 @@
         <v>52.47</v>
       </c>
       <c r="K75">
-        <v>1595.96</v>
+        <v>1595.9625</v>
       </c>
       <c r="L75">
         <v>1095</v>
@@ -7265,7 +7265,7 @@
         <v>25000</v>
       </c>
       <c r="V75">
-        <v>1280.96</v>
+        <v>1280.9625</v>
       </c>
       <c r="Y75">
         <v>2</v>
@@ -7399,7 +7399,7 @@
         <v>472.68</v>
       </c>
       <c r="E77">
-        <v>11.1</v>
+        <v>11.095</v>
       </c>
       <c r="G77">
         <v>2.04</v>
@@ -7435,7 +7435,7 @@
         <v>303</v>
       </c>
       <c r="S77">
-        <v>641</v>
+        <v>641.0033333</v>
       </c>
       <c r="T77">
         <v>27000</v>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD77">
@@ -7512,7 +7512,7 @@
         <v>10750</v>
       </c>
       <c r="D78">
-        <v>86.23999999999999</v>
+        <v>86.235</v>
       </c>
       <c r="G78">
         <v>1.8</v>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AD78">
@@ -7617,7 +7617,7 @@
         <v>4634.4</v>
       </c>
       <c r="D79">
-        <v>45.63</v>
+        <v>45.62666667</v>
       </c>
       <c r="E79">
         <v>3.82</v>
@@ -7632,7 +7632,7 @@
         <v>9.82</v>
       </c>
       <c r="K79">
-        <v>298.69</v>
+        <v>298.6916667</v>
       </c>
       <c r="L79">
         <v>304</v>
@@ -7641,10 +7641,10 @@
         <v>304</v>
       </c>
       <c r="N79">
-        <v>53</v>
+        <v>53.3</v>
       </c>
       <c r="O79">
-        <v>4.94</v>
+        <v>4.9375</v>
       </c>
       <c r="P79">
         <v>1</v>
@@ -7656,13 +7656,13 @@
         <v>48</v>
       </c>
       <c r="S79">
-        <v>104.52</v>
+        <v>104.5156675</v>
       </c>
       <c r="T79">
         <v>1397</v>
       </c>
       <c r="V79">
-        <v>250.69</v>
+        <v>250.6916667</v>
       </c>
       <c r="W79">
         <v>351</v>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD79">
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="C80">
-        <v>161833.33</v>
+        <v>161833.3333</v>
       </c>
       <c r="D80">
         <v>247.21</v>
@@ -7749,7 +7749,7 @@
         <v>1095</v>
       </c>
       <c r="N80">
-        <v>108</v>
+        <v>108.5</v>
       </c>
       <c r="O80">
         <v>2.75</v>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>8.699999999999999</t>
         </is>
       </c>
       <c r="AD80">
@@ -7826,13 +7826,13 @@
         </is>
       </c>
       <c r="C81">
-        <v>3183.33</v>
+        <v>3183.333333</v>
       </c>
       <c r="D81">
-        <v>31.18</v>
+        <v>31.18333333</v>
       </c>
       <c r="E81">
-        <v>5.62</v>
+        <v>5.625</v>
       </c>
       <c r="G81">
         <v>1.5</v>
@@ -7856,7 +7856,7 @@
         <v>56</v>
       </c>
       <c r="S81">
-        <v>107.44</v>
+        <v>107.4375</v>
       </c>
       <c r="W81">
         <v>152</v>
@@ -7889,7 +7889,7 @@
         <v>22909</v>
       </c>
       <c r="AN81">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="AO81">
         <v>80</v>
@@ -7905,7 +7905,7 @@
         <v>63000</v>
       </c>
       <c r="D82">
-        <v>153.26</v>
+        <v>153.265</v>
       </c>
       <c r="G82">
         <v>1.74</v>
@@ -7920,7 +7920,7 @@
         <v>639</v>
       </c>
       <c r="N82">
-        <v>111</v>
+        <v>111.15</v>
       </c>
       <c r="O82">
         <v>2</v>
@@ -7929,7 +7929,7 @@
         <v>1</v>
       </c>
       <c r="Q82">
-        <v>445</v>
+        <v>445.02</v>
       </c>
       <c r="R82">
         <v>265</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>55.00</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AD82">
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="C83">
-        <v>627.3</v>
+        <v>627.3033333</v>
       </c>
       <c r="D83">
         <v>12.51</v>
@@ -8010,13 +8010,13 @@
         <v>730</v>
       </c>
       <c r="M83">
-        <v>351</v>
+        <v>350.57</v>
       </c>
       <c r="N83">
         <v>56</v>
       </c>
       <c r="O83">
-        <v>1.98</v>
+        <v>1.983333333</v>
       </c>
       <c r="P83">
         <v>2</v>
@@ -8025,7 +8025,7 @@
         <v>365</v>
       </c>
       <c r="R83">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="W83">
         <v>2</v>
@@ -8083,7 +8083,7 @@
         <v>4.39</v>
       </c>
       <c r="G84">
-        <v>1.25</v>
+        <v>1.254</v>
       </c>
       <c r="I84">
         <v>40</v>
@@ -8159,7 +8159,7 @@
         <v>1.02</v>
       </c>
       <c r="E85">
-        <v>0.09</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD85">
@@ -8273,7 +8273,7 @@
         <v>2</v>
       </c>
       <c r="W86">
-        <v>0.14</v>
+        <v>0.139</v>
       </c>
       <c r="Y86">
         <v>2</v>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD86">
@@ -8315,7 +8315,7 @@
         <v>3.5</v>
       </c>
       <c r="E87">
-        <v>0.31</v>
+        <v>0.313</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -8327,7 +8327,7 @@
         <v>11.49</v>
       </c>
       <c r="K87">
-        <v>349.49</v>
+        <v>349.4875</v>
       </c>
       <c r="L87">
         <v>253</v>
@@ -8354,7 +8354,7 @@
         <v>235</v>
       </c>
       <c r="V87">
-        <v>307.49</v>
+        <v>307.4875</v>
       </c>
       <c r="W87">
         <v>7</v>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD87">
@@ -8469,7 +8469,7 @@
         <v>3.13</v>
       </c>
       <c r="K89">
-        <v>95.2</v>
+        <v>95.20416667000001</v>
       </c>
       <c r="L89">
         <v>75</v>
@@ -8493,16 +8493,16 @@
         <v>23</v>
       </c>
       <c r="S89">
-        <v>0.9399999999999999</v>
+        <v>0.945</v>
       </c>
       <c r="T89">
         <v>7.7</v>
       </c>
       <c r="V89">
-        <v>72.2</v>
+        <v>72.20416667000001</v>
       </c>
       <c r="W89">
-        <v>0.02</v>
+        <v>0.0235</v>
       </c>
       <c r="Z89">
         <v>2</v>
@@ -8578,7 +8578,7 @@
         <v>8.5</v>
       </c>
       <c r="W90">
-        <v>0.05</v>
+        <v>0.0524</v>
       </c>
       <c r="Y90">
         <v>2</v>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD90">
@@ -8647,7 +8647,7 @@
         <v>9.5</v>
       </c>
       <c r="K91">
-        <v>288.96</v>
+        <v>288.9583333</v>
       </c>
       <c r="L91">
         <v>304</v>
@@ -8665,16 +8665,16 @@
         <v>22</v>
       </c>
       <c r="S91">
-        <v>0.24</v>
+        <v>0.235</v>
       </c>
       <c r="T91">
         <v>5.1</v>
       </c>
       <c r="V91">
-        <v>266.96</v>
+        <v>266.9583333</v>
       </c>
       <c r="W91">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="Y91">
         <v>2</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD91">
@@ -8749,7 +8749,7 @@
         <v>10</v>
       </c>
       <c r="W92">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="Y92">
         <v>2</v>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD92">
@@ -8803,7 +8803,7 @@
         <v>7.7</v>
       </c>
       <c r="G93">
-        <v>1.38</v>
+        <v>1.377</v>
       </c>
       <c r="I93">
         <v>36.8</v>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD93">
@@ -8886,7 +8886,7 @@
         <v>3.5</v>
       </c>
       <c r="G94">
-        <v>1.07</v>
+        <v>1.07063</v>
       </c>
       <c r="I94">
         <v>22.3</v>
@@ -8895,7 +8895,7 @@
         <v>16.18</v>
       </c>
       <c r="K94">
-        <v>492.14</v>
+        <v>492.1416667</v>
       </c>
       <c r="L94">
         <v>365</v>
@@ -8919,7 +8919,7 @@
         <v>80</v>
       </c>
       <c r="V94">
-        <v>355.14</v>
+        <v>355.1416667</v>
       </c>
       <c r="W94">
         <v>3</v>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD94">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD95">
@@ -9043,7 +9043,7 @@
         <v>160.75</v>
       </c>
       <c r="G97">
-        <v>1.02</v>
+        <v>1.019</v>
       </c>
       <c r="I97">
         <v>56</v>
@@ -9052,7 +9052,7 @@
         <v>2251</v>
       </c>
       <c r="M97">
-        <v>2129</v>
+        <v>2129.33</v>
       </c>
       <c r="N97">
         <v>335</v>
@@ -9061,7 +9061,7 @@
         <v>1</v>
       </c>
       <c r="Q97">
-        <v>1247</v>
+        <v>1247.33</v>
       </c>
       <c r="R97">
         <v>456</v>
@@ -9118,13 +9118,13 @@
         <v>3420</v>
       </c>
       <c r="D98">
-        <v>19.17</v>
+        <v>19.16666667</v>
       </c>
       <c r="E98">
         <v>7.75</v>
       </c>
       <c r="G98">
-        <v>1.37</v>
+        <v>1.368</v>
       </c>
       <c r="I98">
         <v>14.8</v>
@@ -9133,7 +9133,7 @@
         <v>71.98999999999999</v>
       </c>
       <c r="K98">
-        <v>2189.7</v>
+        <v>2189.695833</v>
       </c>
       <c r="L98">
         <v>500</v>
@@ -9157,13 +9157,13 @@
         <v>116</v>
       </c>
       <c r="S98">
-        <v>202.33</v>
+        <v>202.3333333</v>
       </c>
       <c r="T98">
         <v>500</v>
       </c>
       <c r="V98">
-        <v>2073.7</v>
+        <v>2073.695833</v>
       </c>
       <c r="W98">
         <v>0.26</v>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AD98">
@@ -9217,7 +9217,7 @@
         <v>3775000</v>
       </c>
       <c r="D99">
-        <v>5253.56</v>
+        <v>5253.555556</v>
       </c>
       <c r="E99">
         <v>1650</v>
@@ -9256,7 +9256,7 @@
         <v>1071</v>
       </c>
       <c r="S99">
-        <v>110333.33</v>
+        <v>110333.3333</v>
       </c>
       <c r="T99">
         <v>600000</v>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AE99">
@@ -9316,7 +9316,7 @@
         <v>10.5</v>
       </c>
       <c r="K100">
-        <v>319.38</v>
+        <v>319.375</v>
       </c>
       <c r="L100">
         <v>274</v>
@@ -9340,17 +9340,17 @@
         <v>315</v>
       </c>
       <c r="S100">
-        <v>0.43</v>
+        <v>0.429</v>
       </c>
       <c r="T100">
         <v>3000</v>
       </c>
       <c r="V100">
-        <v>4.38</v>
+        <v>4.375</v>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AG100">
@@ -9385,7 +9385,7 @@
         <v>20</v>
       </c>
       <c r="K101">
-        <v>608.33</v>
+        <v>608.3333333</v>
       </c>
       <c r="L101">
         <v>670</v>
@@ -9406,13 +9406,13 @@
         <v>540</v>
       </c>
       <c r="S101">
-        <v>0.93</v>
+        <v>0.93443</v>
       </c>
       <c r="T101">
         <v>11000</v>
       </c>
       <c r="V101">
-        <v>68.33</v>
+        <v>68.33333333</v>
       </c>
       <c r="W101">
         <v>236</v>
@@ -9452,7 +9452,7 @@
         <v>16.5</v>
       </c>
       <c r="K102">
-        <v>501.88</v>
+        <v>501.875</v>
       </c>
       <c r="L102">
         <v>395</v>
@@ -9476,13 +9476,13 @@
         <v>187</v>
       </c>
       <c r="S102">
-        <v>0.6</v>
+        <v>0.598</v>
       </c>
       <c r="T102">
         <v>1483</v>
       </c>
       <c r="V102">
-        <v>314.88</v>
+        <v>314.875</v>
       </c>
       <c r="W102">
         <v>13</v>
@@ -9527,7 +9527,7 @@
         <v>6.11</v>
       </c>
       <c r="K103">
-        <v>185.85</v>
+        <v>185.8458333</v>
       </c>
       <c r="L103">
         <v>184</v>
@@ -9551,13 +9551,13 @@
         <v>102</v>
       </c>
       <c r="S103">
-        <v>0.15</v>
+        <v>0.147</v>
       </c>
       <c r="T103">
         <v>142.5</v>
       </c>
       <c r="V103">
-        <v>83.84999999999999</v>
+        <v>83.84583333</v>
       </c>
       <c r="W103">
         <v>51</v>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AG103">
@@ -9590,6 +9590,20 @@
       </c>
       <c r="AO103">
         <v>102</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>¶ See Table S2 for column definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>*Calculated from images of Nissl-stained coronal sections from www.brainmuseum.org (see Methods)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -9873,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FDC06F6-63EC-4C89-BFA8-69E4DEACA3ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44C7DDF0-B32C-4E2F-9936-EF0CAB68880A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04448C68-C568-4779-A830-B3037BD49537}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA061AED-5ED8-46C1-82F0-B1D593A80FAC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E55ED338-84E1-4810-A5FF-26DE88EA7F56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF4D92BD-1F04-4EAF-9DE8-A64B6BE1EF06}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44C7DDF0-B32C-4E2F-9936-EF0CAB68880A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F5CF888-7AE0-4234-A808-9AC88891EDB0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA061AED-5ED8-46C1-82F0-B1D593A80FAC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB50B76B-67F3-42FF-81F7-3BDB0E6A0441}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF4D92BD-1F04-4EAF-9DE8-A64B6BE1EF06}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54F2A531-2CDC-4E7F-A058-32AF2FA3961C}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9609,291 +9609,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D5154F1-CBA3-43CC-94C2-296D05052756}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE6EFC03-B7EB-455F-BA13-564187AE0960}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46F6AF2C-771F-4AE7-90DA-E3BBE6695956}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9609,4 +9609,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7FAA75F-25F5-43DA-9A3E-24542D343B82}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5840350C-35F9-42AE-96FD-719B8D4BC39B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C358F35-851E-4F73-B420-A1B1F6583468}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7FAA75F-25F5-43DA-9A3E-24542D343B82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BD865BC-507A-4933-9699-2614343CDC2A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5840350C-35F9-42AE-96FD-719B8D4BC39B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD02A4E5-99C3-4575-B1F2-C3DA70706224}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C358F35-851E-4F73-B420-A1B1F6583468}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1A08C7E-117B-47F2-9F77-1BBF24FC41F9}"/>
 </file>